--- a/Docs/Diferencies entre PiGs Meus i Self.xlsx
+++ b/Docs/Diferencies entre PiGs Meus i Self.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Repositoris\C#\Meus\InversionsV2\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA9DC4B-749A-4B06-A6B7-9D286E0DFFCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71836F31-A402-4074-BC26-05E3D274F1E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{6BF5068B-93F7-4D64-8F2C-C2F86CB2EFAE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{6BF5068B-93F7-4D64-8F2C-C2F86CB2EFAE}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="PiGs 12-12-2022" sheetId="3" r:id="rId1"/>
+    <sheet name="PiGs 03-11-2022" sheetId="1" r:id="rId2"/>
+    <sheet name="Accions" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,40 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
-  <si>
-    <t>19-NB Capital Plus FI</t>
-  </si>
-  <si>
-    <t>ES0125240038</t>
-  </si>
-  <si>
-    <t>5-Deutschland</t>
-  </si>
-  <si>
-    <t>DE0008490962</t>
-  </si>
-  <si>
-    <t>28-Aberdeen Standard Liquidity Fund Euro Fund A-2 Ac</t>
-  </si>
-  <si>
-    <t>LU0090865873</t>
-  </si>
-  <si>
-    <t>27-Global Technology A-Acc-EUR</t>
-  </si>
-  <si>
-    <t>LU1213836080</t>
-  </si>
-  <si>
-    <t>16-DWS Aktien Strategie Deutschland</t>
-  </si>
-  <si>
-    <t>30-BGF World Energy E2</t>
-  </si>
-  <si>
-    <t>1036-CS (Lux) Commodity Idx Plus USD B</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="29">
   <si>
     <t>Total</t>
   </si>
@@ -78,14 +47,90 @@
   </si>
   <si>
     <t>Dif</t>
+  </si>
+  <si>
+    <t>Threadneedle (Lux) Enhanced Cmdts</t>
+  </si>
+  <si>
+    <t>CS (Lux) Commodity Idx Plus USD B</t>
+  </si>
+  <si>
+    <t>Aberdeen Standard Liquidity Fund Euro Fund A-2 Ac</t>
+  </si>
+  <si>
+    <t>Global Technology A-Acc-EUR</t>
+  </si>
+  <si>
+    <t>DWS Aktien Strategie Deutschland</t>
+  </si>
+  <si>
+    <t>BGF World Energy E2</t>
+  </si>
+  <si>
+    <t>NB Capital Plus FI</t>
+  </si>
+  <si>
+    <t>Deutschland</t>
+  </si>
+  <si>
+    <t>Import Compra Orig Meu</t>
+  </si>
+  <si>
+    <t>Import Compra Orig Self</t>
+  </si>
+  <si>
+    <t>Threadneedle (Lux) Enhanced</t>
+  </si>
+  <si>
+    <t>Optimal Income A-H Grs Acc Hdg EUR</t>
+  </si>
+  <si>
+    <t>Total Return N Acc €-H1</t>
+  </si>
+  <si>
+    <t>Biotechnology C USD Acc</t>
+  </si>
+  <si>
+    <t>European Growth N Acc ?</t>
+  </si>
+  <si>
+    <t>Bolsa Tecnología y Telecomunicaciones FI</t>
+  </si>
+  <si>
+    <t>Imp compra Orig App</t>
+  </si>
+  <si>
+    <t>Prod</t>
+  </si>
+  <si>
+    <t>Prod Orig</t>
+  </si>
+  <si>
+    <t>Productes actuals amb desgloç de compres originals</t>
+  </si>
+  <si>
+    <t>Productes actuals amb compres originals</t>
+  </si>
+  <si>
+    <t>Productes originals amb participacions en cartera</t>
+  </si>
+  <si>
+    <t>Imp compra Orig Self</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Abrdn US Dollar Fund A-2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;€&quot;;[Red]\-#,##0.00\ &quot;€&quot;"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -104,12 +149,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -124,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="8" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -132,6 +183,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -150,9 +209,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de l'Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Oficina">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -190,7 +249,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Oficina">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -296,7 +355,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Oficina">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -445,161 +504,1292 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA6E2FDD-37DA-447A-A5FE-605F87D6A64A}">
-  <dimension ref="A1:E9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF8A5D0D-B8B5-43EE-9A3C-77A80F538C29}">
+  <dimension ref="A1:G54"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="47.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33" customWidth="1"/>
+    <col min="2" max="3" width="13.7265625" customWidth="1"/>
+    <col min="4" max="4" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="1.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="C1" s="4" t="s">
+    <row r="1" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="5">
+        <v>44907</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="C1" s="6" t="s">
         <v>13</v>
       </c>
+      <c r="D1" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="E1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="1">
+        <v>777.36049221571</v>
+      </c>
+      <c r="C2" s="1">
+        <v>777.35</v>
+      </c>
+      <c r="D2" s="1">
+        <f t="shared" ref="D2:D8" si="0">+B2-C2</f>
+        <v>1.0492215709973607E-2</v>
+      </c>
+      <c r="E2" s="1">
+        <v>350.35</v>
+      </c>
+      <c r="F2" s="1">
+        <v>350.36</v>
+      </c>
+      <c r="G2" s="1">
+        <f t="shared" ref="G2:G8" si="1">+E2-F2</f>
+        <v>-9.9999999999909051E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1856.35</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1861.77</v>
+      </c>
+      <c r="D3" s="1">
+        <f t="shared" si="0"/>
+        <v>-5.4200000000000728</v>
+      </c>
+      <c r="E3" s="1">
+        <v>748.54</v>
+      </c>
+      <c r="F3" s="1">
+        <v>743.12</v>
+      </c>
+      <c r="G3" s="1">
+        <f t="shared" si="1"/>
+        <v>5.4199999999999591</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1">
+        <v>31915.82</v>
+      </c>
+      <c r="C4" s="1">
+        <v>30830.71</v>
+      </c>
+      <c r="D4" s="1">
+        <f t="shared" si="0"/>
+        <v>1085.1100000000006</v>
+      </c>
+      <c r="E4" s="1">
+        <v>41476.33</v>
+      </c>
+      <c r="F4" s="1">
+        <v>42561.45</v>
+      </c>
+      <c r="G4" s="1">
+        <f t="shared" si="1"/>
+        <v>-1085.1199999999953</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1">
+        <v>5754.79</v>
+      </c>
+      <c r="C5" s="1">
+        <v>5755.81</v>
+      </c>
+      <c r="D5" s="1">
+        <f t="shared" si="0"/>
+        <v>-1.0200000000004366</v>
+      </c>
+      <c r="E5" s="1">
+        <v>13810.84</v>
+      </c>
+      <c r="F5" s="1">
+        <v>13809.82</v>
+      </c>
+      <c r="G5" s="1">
+        <f t="shared" si="1"/>
+        <v>1.0200000000004366</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1">
+        <v>365.32</v>
+      </c>
+      <c r="C6" s="1">
+        <v>365.18</v>
+      </c>
+      <c r="D6" s="1">
+        <f t="shared" si="0"/>
+        <v>0.13999999999998636</v>
+      </c>
+      <c r="E6" s="1">
+        <v>372.34</v>
+      </c>
+      <c r="F6" s="1">
+        <v>372.47</v>
+      </c>
+      <c r="G6" s="1">
+        <f t="shared" si="1"/>
+        <v>-0.1300000000000523</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1">
+        <v>5237.3599999999997</v>
+      </c>
+      <c r="C7" s="1">
+        <v>5235.45</v>
+      </c>
+      <c r="D7" s="1">
+        <f t="shared" si="0"/>
+        <v>1.9099999999998545</v>
+      </c>
+      <c r="E7" s="1">
+        <v>5573.34</v>
+      </c>
+      <c r="F7" s="1">
+        <v>5575.25</v>
+      </c>
+      <c r="G7" s="1">
+        <f t="shared" si="1"/>
+        <v>-1.9099999999998545</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="2">
+        <f>SUM(B2:B7)</f>
+        <v>45907.00049221571</v>
+      </c>
+      <c r="C8" s="2">
+        <f>SUM(C2:C7)</f>
+        <v>44826.27</v>
+      </c>
+      <c r="D8" s="2">
+        <f t="shared" si="0"/>
+        <v>1080.7304922157127</v>
+      </c>
+      <c r="E8" s="2">
+        <f>SUM(E2:E7)</f>
+        <v>62331.739999999991</v>
+      </c>
+      <c r="F8" s="2">
+        <f>SUM(F2:F7)</f>
+        <v>63412.47</v>
+      </c>
+      <c r="G8" s="2">
+        <f t="shared" si="1"/>
+        <v>-1080.7300000000105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="7">
+        <v>1000</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="7">
+        <v>366.05200000000002</v>
+      </c>
+      <c r="D15" s="7">
+        <f>+C15</f>
+        <v>366.05200000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="7">
+        <v>222.61600000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="7">
+        <v>273.11200000000002</v>
+      </c>
+      <c r="D17" s="7">
+        <f>+C17</f>
+        <v>273.11200000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="7"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="7">
+        <v>777.36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="7"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="7">
+        <v>2897.3580000000002</v>
+      </c>
+      <c r="D21" s="7">
+        <f>+C21</f>
+        <v>2897.3580000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="9" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1">
-        <v>1854.47</v>
-      </c>
-      <c r="D2" s="1">
-        <v>2551.2199999999998</v>
-      </c>
-      <c r="E2" s="1">
-        <f>+C2-D2</f>
-        <v>-696.74999999999977</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1">
-        <v>156.88999999999999</v>
-      </c>
-      <c r="D3" s="1">
-        <v>156.9</v>
-      </c>
-      <c r="E3" s="1">
-        <f t="shared" ref="E3:E9" si="0">+C3-D3</f>
-        <v>-1.0000000000019327E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="C22" s="7"/>
+      <c r="E22" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="7">
+        <v>7395.8220000000001</v>
+      </c>
+      <c r="E23" s="7">
+        <f>C23</f>
+        <v>7395.8220000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B24" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="7">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="D24" s="7">
+        <f>+C24</f>
+        <v>5.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="7"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="7">
+        <v>4480.9009999999998</v>
+      </c>
+      <c r="D26" s="7">
+        <f>+C26</f>
+        <v>4480.9009999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B27" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="7">
+        <v>5511.21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="7">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="7">
+        <v>7841.5749999999998</v>
+      </c>
+      <c r="D29" s="7">
+        <f>+C29</f>
+        <v>7841.5749999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="7">
+        <v>2785.4949999999999</v>
+      </c>
+      <c r="D30" s="7">
+        <f>+C30</f>
+        <v>2785.4949999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="7"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" s="7">
+        <v>4043.9810000000002</v>
+      </c>
+      <c r="D32" s="7">
+        <f>+C32</f>
+        <v>4043.9810000000002</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="7">
+        <v>1710.337</v>
+      </c>
+      <c r="D33" s="7">
+        <f>+C33</f>
+        <v>1710.337</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="7"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" s="7">
+        <v>365.21600000000001</v>
+      </c>
+      <c r="D35" s="7">
+        <f>+C35</f>
+        <v>365.21600000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="7"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" s="7">
+        <v>5235.9089999999997</v>
+      </c>
+      <c r="D37" s="7">
+        <f>+C37</f>
+        <v>5235.9089999999997</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C38" s="8">
+        <f>SUM(C14:C37)</f>
+        <v>45906.996999999996</v>
+      </c>
+      <c r="D38" s="8">
+        <f>SUM(D13:D37)</f>
+        <v>29999.988999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="1">
-        <v>7180.02</v>
-      </c>
-      <c r="D4" s="1">
-        <v>7180.02</v>
-      </c>
-      <c r="E4" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="1">
-        <v>34127.129999999997</v>
-      </c>
-      <c r="D5" s="1">
-        <v>34510.11</v>
-      </c>
-      <c r="E5" s="1">
-        <f t="shared" si="0"/>
-        <v>-382.9800000000032</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="1">
-        <v>12966.15</v>
-      </c>
-      <c r="D6" s="1">
-        <v>12965.13</v>
-      </c>
-      <c r="E6" s="1">
-        <f t="shared" si="0"/>
-        <v>1.0200000000004366</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="1">
-        <v>259</v>
-      </c>
-      <c r="D7" s="1">
-        <v>259.13</v>
-      </c>
-      <c r="E7" s="1">
-        <f t="shared" si="0"/>
-        <v>-0.12999999999999545</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="1">
-        <v>5851.94</v>
-      </c>
-      <c r="D8" s="1">
-        <v>5853.83</v>
-      </c>
-      <c r="E8" s="1">
-        <f t="shared" si="0"/>
-        <v>-1.8900000000003274</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="2">
-        <f>SUM(C2:C8)</f>
-        <v>62395.6</v>
-      </c>
-      <c r="D9" s="2">
-        <f>SUM(D2:D8)</f>
-        <v>63476.34</v>
-      </c>
-      <c r="E9" s="2">
-        <f t="shared" si="0"/>
-        <v>-1080.739999999998</v>
-      </c>
+      <c r="B42" s="7">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>17</v>
+      </c>
+      <c r="B43" s="7">
+        <v>5511.21</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" s="7">
+        <v>999.976</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B45" s="10">
+        <v>19999.989000000001</v>
+      </c>
+      <c r="C45" s="7">
+        <f>+B45+B46</f>
+        <v>29999.988000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B46" s="10">
+        <v>9999.9989999999998</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>18</v>
+      </c>
+      <c r="B47" s="7">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>19</v>
+      </c>
+      <c r="B48" s="7">
+        <v>7395.8220000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B49" s="8">
+        <f>SUM(B42:B48)</f>
+        <v>45906.995999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B53" s="8">
+        <v>42086.609398132998</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B54" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA6E2FDD-37DA-447A-A5FE-605F87D6A64A}">
+  <dimension ref="A1:G68"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="33" customWidth="1"/>
+    <col min="2" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="1.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="5">
+        <v>44868</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1861.77942651227</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1861.77</v>
+      </c>
+      <c r="D2" s="1">
+        <f>+B2-C2</f>
+        <v>9.4265122700107895E-3</v>
+      </c>
+      <c r="E2" s="1">
+        <v>896.66</v>
+      </c>
+      <c r="F2" s="1">
+        <v>891.27</v>
+      </c>
+      <c r="G2" s="1">
+        <f>+E2-F2</f>
+        <v>5.3899999999999864</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1">
+        <v>777.36049221571</v>
+      </c>
+      <c r="C3" s="1">
+        <v>777.35</v>
+      </c>
+      <c r="D3" s="1">
+        <f t="shared" ref="D3:D10" si="0">+B3-C3</f>
+        <v>1.0492215709973607E-2</v>
+      </c>
+      <c r="E3" s="1">
+        <v>256.39999999999998</v>
+      </c>
+      <c r="F3" s="1">
+        <v>256.39999999999998</v>
+      </c>
+      <c r="G3" s="1">
+        <f t="shared" ref="G3:G5" si="1">+E3-F3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1">
+        <v>2897.3580237798001</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2897.36</v>
+      </c>
+      <c r="D4" s="1">
+        <f t="shared" si="0"/>
+        <v>-1.9762202000492834E-3</v>
+      </c>
+      <c r="E4" s="1">
+        <v>6771.2</v>
+      </c>
+      <c r="F4" s="1">
+        <v>6771.2</v>
+      </c>
+      <c r="G4" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>7395.8748393039796</v>
+      </c>
+      <c r="C5" s="1">
+        <v>6693.74</v>
+      </c>
+      <c r="D5" s="1">
+        <f t="shared" si="0"/>
+        <v>702.13483930397979</v>
+      </c>
+      <c r="E5" s="1">
+        <v>944.42</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1646.6</v>
+      </c>
+      <c r="G5" s="1">
+        <f t="shared" si="1"/>
+        <v>-702.18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1">
+        <v>21619.181022556499</v>
+      </c>
+      <c r="C6" s="1">
+        <v>21239.61</v>
+      </c>
+      <c r="D6" s="1">
+        <f t="shared" si="0"/>
+        <v>379.57102255649806</v>
+      </c>
+      <c r="E6" s="1">
+        <v>34148.36</v>
+      </c>
+      <c r="F6" s="1">
+        <v>34531.339999999997</v>
+      </c>
+      <c r="G6" s="1">
+        <f t="shared" ref="G6:G10" si="2">+E6-F6</f>
+        <v>-382.97999999999593</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1">
+        <v>5754.3174082974501</v>
+      </c>
+      <c r="C7" s="1">
+        <v>5755.81</v>
+      </c>
+      <c r="D7" s="1">
+        <f t="shared" si="0"/>
+        <v>-1.4925917025502713</v>
+      </c>
+      <c r="E7" s="1">
+        <v>13583.19</v>
+      </c>
+      <c r="F7" s="1">
+        <v>13582.17</v>
+      </c>
+      <c r="G7" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0200000000004366</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1">
+        <v>365.215777443364</v>
+      </c>
+      <c r="C8" s="1">
+        <v>365.18</v>
+      </c>
+      <c r="D8" s="1">
+        <f t="shared" si="0"/>
+        <v>3.5777443363997463E-2</v>
+      </c>
+      <c r="E8" s="1">
+        <v>313.20999999999998</v>
+      </c>
+      <c r="F8" s="1">
+        <v>313.35000000000002</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" si="2"/>
+        <v>-0.1400000000000432</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1">
+        <v>5235.9091225654602</v>
+      </c>
+      <c r="C9" s="1">
+        <v>5235.45</v>
+      </c>
+      <c r="D9" s="1">
+        <f t="shared" si="0"/>
+        <v>0.45912256546034769</v>
+      </c>
+      <c r="E9" s="1">
+        <v>6871.1</v>
+      </c>
+      <c r="F9" s="1">
+        <v>6873.02</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="2"/>
+        <v>-1.9200000000000728</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="2">
+        <f>SUM(B2:B9)</f>
+        <v>45906.99611267454</v>
+      </c>
+      <c r="C10" s="2">
+        <f>SUM(C2:C9)</f>
+        <v>44826.27</v>
+      </c>
+      <c r="D10" s="2">
+        <f t="shared" si="0"/>
+        <v>1080.7261126745434</v>
+      </c>
+      <c r="E10" s="2">
+        <f>SUM(E2:E9)</f>
+        <v>63784.54</v>
+      </c>
+      <c r="F10" s="2">
+        <f>SUM(F2:F9)</f>
+        <v>64865.349999999991</v>
+      </c>
+      <c r="G10" s="2">
+        <f t="shared" si="2"/>
+        <v>-1080.8099999999904</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="3"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="7">
+        <v>1861.779</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="7">
+        <v>777.36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="7">
+        <v>2897.3580000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="7">
+        <v>7395.875</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="7">
+        <v>21619.181</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="7">
+        <v>5754.317</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="7">
+        <v>365.21600000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>5235.9089999999997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B23" s="8">
+        <f>SUM(B15:B22)</f>
+        <v>45906.995000000003</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="7">
+        <v>1000</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="7">
+        <v>366.05200000000002</v>
+      </c>
+      <c r="D29" s="7">
+        <f>+C29</f>
+        <v>366.05200000000002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B30" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="7">
+        <v>222.61600000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" s="7">
+        <v>273.11200000000002</v>
+      </c>
+      <c r="D31" s="7">
+        <f>+C31</f>
+        <v>273.11200000000002</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" s="7">
+        <v>777.36</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="7"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" s="7">
+        <v>2897.3580000000002</v>
+      </c>
+      <c r="D35" s="7">
+        <f>+C35</f>
+        <v>2897.3580000000002</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="7"/>
+      <c r="E36" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B37" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="7">
+        <v>7395.8220000000001</v>
+      </c>
+      <c r="E37" s="7">
+        <f>C37</f>
+        <v>7395.8220000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B38" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" s="7">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="D38" s="7">
+        <f>+C38</f>
+        <v>5.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="7"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" s="7">
+        <v>4480.9009999999998</v>
+      </c>
+      <c r="D40" s="7">
+        <f>+C40</f>
+        <v>4480.9009999999998</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B41" t="s">
+        <v>17</v>
+      </c>
+      <c r="C41" s="7">
+        <v>5511.21</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B42" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="7">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" s="7">
+        <v>7841.5749999999998</v>
+      </c>
+      <c r="D43" s="7">
+        <f>+C43</f>
+        <v>7841.5749999999998</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" s="7">
+        <v>2785.4949999999999</v>
+      </c>
+      <c r="D44" s="7">
+        <f>+C44</f>
+        <v>2785.4949999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="7"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" s="7">
+        <v>4043.9810000000002</v>
+      </c>
+      <c r="D46" s="7">
+        <f>+C46</f>
+        <v>4043.9810000000002</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" s="7">
+        <v>1710.337</v>
+      </c>
+      <c r="D47" s="7">
+        <f>+C47</f>
+        <v>1710.337</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="7"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" s="7">
+        <v>365.21600000000001</v>
+      </c>
+      <c r="D49" s="7">
+        <f>+C49</f>
+        <v>365.21600000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50" s="7"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" s="7">
+        <v>5235.9089999999997</v>
+      </c>
+      <c r="D51" s="7">
+        <f>+C51</f>
+        <v>5235.9089999999997</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C52" s="8">
+        <f>SUM(C28:C51)</f>
+        <v>45906.996999999996</v>
+      </c>
+      <c r="D52" s="8">
+        <f>SUM(D27:D51)</f>
+        <v>29999.988999999998</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>10</v>
+      </c>
+      <c r="B56" s="7">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>17</v>
+      </c>
+      <c r="B57" s="7">
+        <v>5511.21</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" s="7">
+        <v>999.976</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B59" s="10">
+        <v>19999.989000000001</v>
+      </c>
+      <c r="C59" s="7">
+        <f>+B59+B60</f>
+        <v>29999.988000000001</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B60" s="10">
+        <v>9999.9989999999998</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>18</v>
+      </c>
+      <c r="B61" s="7">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>19</v>
+      </c>
+      <c r="B62" s="7">
+        <v>7395.8220000000001</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B63" s="8">
+        <f>SUM(B56:B62)</f>
+        <v>45906.995999999999</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B67" s="8">
+        <v>42086.609398132998</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B68" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{996BBA40-DCEF-47E5-85BB-56C68AEE75F0}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Docs/Diferencies entre PiGs Meus i Self.xlsx
+++ b/Docs/Diferencies entre PiGs Meus i Self.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Repositoris\C#\Meus\InversionsV2\Docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Repositoris\C#\_Actiu\InversionsV2\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71836F31-A402-4074-BC26-05E3D274F1E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B198EF06-C5FD-42D9-861E-0244AC932116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{6BF5068B-93F7-4D64-8F2C-C2F86CB2EFAE}"/>
+    <workbookView xWindow="19090" yWindow="-20" windowWidth="19420" windowHeight="10420" xr2:uid="{6BF5068B-93F7-4D64-8F2C-C2F86CB2EFAE}"/>
   </bookViews>
   <sheets>
     <sheet name="PiGs 12-12-2022" sheetId="3" r:id="rId1"/>
@@ -21,14 +21,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -505,7 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF8A5D0D-B8B5-43EE-9A3C-77A80F538C29}">
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="33" customWidth="1"/>
@@ -514,7 +506,7 @@
     <col min="8" max="8" width="1.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="5">
         <v>44907</v>
       </c>
@@ -537,7 +529,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -562,7 +554,7 @@
         <v>-9.9999999999909051E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -587,7 +579,7 @@
         <v>5.4199999999999591</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -612,7 +604,7 @@
         <v>-1085.1199999999953</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -637,7 +629,7 @@
         <v>1.0200000000004366</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -662,7 +654,7 @@
         <v>-0.1300000000000523</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -687,7 +679,7 @@
         <v>-1.9099999999998545</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>0</v>
       </c>
@@ -716,14 +708,14 @@
         <v>-1080.7300000000105</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>21</v>
       </c>
@@ -734,12 +726,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="J13" s="1">
+        <v>1160.78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>10</v>
       </c>
@@ -750,7 +745,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>16</v>
       </c>
@@ -762,7 +757,7 @@
         <v>366.05200000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>15</v>
       </c>
